--- a/FIIN.xlsx
+++ b/FIIN.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://methalc.sharepoint.com/sites/COMERCIAL_/Documentos Compartilhados/FICHA INTRODUÇÃO ITEM NOVO - FIIN/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme\OneDrive\Desktop\gui\Programas\python\ExcelPython\Mehtal_v.1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3DFD85F0-C292-403E-B188-5580994C8A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB8ACCF8-AC2E-4322-A956-3F860108A518}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C63FBA-8DFB-4185-B2E7-A5CD53697551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FOR.ENG.03" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'FOR.ENG.03'!$B$2:$I$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'FOR.ENG.03'!$B$2:$L$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,12 +28,15 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>Data:</t>
   </si>
@@ -47,12 +50,6 @@
     <t>Especificações técnicas</t>
   </si>
   <si>
-    <t>ITEM NOVO</t>
-  </si>
-  <si>
-    <t>MODIFICAÇÃO</t>
-  </si>
-  <si>
     <t>Assinatura:</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
     <t>Observações:</t>
   </si>
   <si>
-    <t>SUBSTITUIÇÃO</t>
-  </si>
-  <si>
     <t>Tipo de Embalagem:</t>
   </si>
   <si>
@@ -89,18 +83,9 @@
     <t>Projeto:</t>
   </si>
   <si>
-    <t>Data de Nomeação:</t>
-  </si>
-  <si>
     <t>Descrição:</t>
   </si>
   <si>
-    <t>Código:</t>
-  </si>
-  <si>
-    <t>Localização:</t>
-  </si>
-  <si>
     <t xml:space="preserve">Planta: </t>
   </si>
   <si>
@@ -143,9 +128,6 @@
     <t>Requisitos específicos</t>
   </si>
   <si>
-    <t>Nº Pedido:</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -173,9 +155,6 @@
     <t>Lote Mínimo Peças:</t>
   </si>
   <si>
-    <t>ATIVAR ITEM OBSOLETO</t>
-  </si>
-  <si>
     <t>DADOS DE CONTRATO:</t>
   </si>
   <si>
@@ -188,46 +167,43 @@
     <t>Lucimara S. Monteiro</t>
   </si>
   <si>
-    <t>MAN LATIN AMERICA LTDA</t>
-  </si>
-  <si>
-    <t>REZENDE</t>
-  </si>
-  <si>
-    <t>REZENDE - RJ</t>
-  </si>
-  <si>
-    <t>VINICIUS ORLANDO</t>
-  </si>
-  <si>
-    <t>20 SEMANAS</t>
-  </si>
-  <si>
     <t>UTIÇLIZA</t>
   </si>
   <si>
-    <t>PCTE ESTAMP</t>
-  </si>
-  <si>
-    <t>REFORÇO</t>
-  </si>
-  <si>
-    <t>Revisão:  25/05/2011</t>
-  </si>
-  <si>
-    <t>GLT1185</t>
-  </si>
-  <si>
-    <t>05 ANOS</t>
-  </si>
-  <si>
-    <t>Cliente: 2V282119D</t>
-  </si>
-  <si>
-    <t>Methal Company: 0103.00682</t>
-  </si>
-  <si>
     <t>Volume anual: 13.266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methal Company: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cliente: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITEM NOVO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MODIFICAÇÃO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUBSTITUIÇÃO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATIVAR ITEM OBSOLETO </t>
+  </si>
+  <si>
+    <t>Revisão:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código:   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nº Pedido:  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data de Nomeação:  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localização:  </t>
   </si>
 </sst>
 </file>
@@ -237,7 +213,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -269,6 +245,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -278,7 +260,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -403,11 +385,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -432,9 +429,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -456,7 +450,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -469,9 +462,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -508,19 +498,109 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -533,21 +613,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -566,78 +640,42 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -653,6 +691,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -662,6 +703,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -676,6 +720,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -703,34 +768,18 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -755,7 +804,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
@@ -776,8 +825,8 @@
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>869282</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>469232</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
@@ -840,274 +889,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>790575</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>180975</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>295275</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3093" name="Check Box 21" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3093"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000150C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>971550</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1171575</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>295275</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3094" name="Check Box 22" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3094"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000160C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>1047750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>295275</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3095" name="Check Box 23" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3095"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000170C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>762000</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>114300</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>952500</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>304800</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3096" name="Check Box 24" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3096"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000180C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
@@ -1187,8 +968,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>247650</xdr:rowOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1246,13 +1027,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>238125</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>238125</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>419100</xdr:colOff>
           <xdr:row>10</xdr:row>
           <xdr:rowOff>219075</xdr:rowOff>
@@ -1313,16 +1094,16 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>238125</xdr:colOff>
           <xdr:row>11</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>419100</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>247650</xdr:rowOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1380,13 +1161,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>7</xdr:col>
+          <xdr:col>10</xdr:col>
           <xdr:colOff>561975</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>238125</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>7</xdr:col>
+          <xdr:col>10</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
           <xdr:row>10</xdr:row>
           <xdr:rowOff>219075</xdr:rowOff>
@@ -1447,13 +1228,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>7</xdr:col>
+          <xdr:col>10</xdr:col>
           <xdr:colOff>561975</xdr:colOff>
           <xdr:row>11</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>7</xdr:col>
+          <xdr:col>10</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
           <xdr:row>11</xdr:row>
           <xdr:rowOff>238125</xdr:rowOff>
@@ -1514,13 +1295,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>2</xdr:col>
+          <xdr:col>3</xdr:col>
           <xdr:colOff>381000</xdr:colOff>
           <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
+          <xdr:col>3</xdr:col>
           <xdr:colOff>561975</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
@@ -1581,13 +1362,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>219075</xdr:colOff>
           <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>409575</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
@@ -1648,13 +1429,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>6</xdr:col>
+          <xdr:col>9</xdr:col>
           <xdr:colOff>533400</xdr:colOff>
           <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>6</xdr:col>
+          <xdr:col>9</xdr:col>
           <xdr:colOff>695325</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
@@ -1715,13 +1496,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>2</xdr:col>
+          <xdr:col>3</xdr:col>
           <xdr:colOff>381000</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
+          <xdr:col>3</xdr:col>
           <xdr:colOff>561975</xdr:colOff>
           <xdr:row>53</xdr:row>
           <xdr:rowOff>28575</xdr:rowOff>
@@ -1782,13 +1563,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>219075</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>409575</xdr:colOff>
           <xdr:row>53</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -1849,13 +1630,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>6</xdr:col>
+          <xdr:col>9</xdr:col>
           <xdr:colOff>533400</xdr:colOff>
           <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>6</xdr:col>
+          <xdr:col>9</xdr:col>
           <xdr:colOff>723900</xdr:colOff>
           <xdr:row>53</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
@@ -1916,14 +1697,14 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>7</xdr:col>
+          <xdr:col>10</xdr:col>
           <xdr:colOff>666750</xdr:colOff>
           <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>828675</xdr:colOff>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>47625</xdr:colOff>
           <xdr:row>51</xdr:row>
           <xdr:rowOff>200025</xdr:rowOff>
         </xdr:to>
@@ -1983,13 +1764,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
           <xdr:row>15</xdr:row>
           <xdr:rowOff>47625</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>466725</xdr:colOff>
           <xdr:row>16</xdr:row>
           <xdr:rowOff>104775</xdr:rowOff>
@@ -2397,783 +2178,928 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:I60"/>
+  <dimension ref="B2:R60"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.140625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="7" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="12" max="12" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="38" t="s">
+    <row r="2" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+    </row>
+    <row r="3" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+    </row>
+    <row r="4" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+    </row>
+    <row r="5" spans="2:18" s="6" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B5" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="50"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="50"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="50"/>
+      <c r="J5" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="57"/>
+      <c r="L5" s="50"/>
+    </row>
+    <row r="6" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="42"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="109"/>
+      <c r="L6" s="110"/>
+    </row>
+    <row r="7" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-    </row>
-    <row r="3" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-    </row>
-    <row r="4" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-    </row>
-    <row r="5" spans="2:9" s="6" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="22" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="113" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="114"/>
+      <c r="K7" s="109"/>
+      <c r="L7" s="110"/>
+      <c r="Q7" s="7"/>
+    </row>
+    <row r="8" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="54"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="108"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="109"/>
+      <c r="L8" s="110"/>
+    </row>
+    <row r="9" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="60"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="23"/>
-    </row>
-    <row r="6" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="59" t="s">
+      <c r="E9" s="54"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="60"/>
-      <c r="E6" s="17" t="s">
+      <c r="H9" s="45"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="111"/>
+      <c r="L9" s="112"/>
+      <c r="R9" s="7"/>
+    </row>
+    <row r="10" spans="2:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="75"/>
+    </row>
+    <row r="11" spans="2:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="E11" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="J11" s="72" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="72"/>
+    </row>
+    <row r="12" spans="2:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="E12" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="J12" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="72"/>
+    </row>
+    <row r="13" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="64"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="70"/>
+    </row>
+    <row r="14" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="64"/>
-    </row>
-    <row r="7" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="62"/>
-      <c r="E7" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="63">
-        <v>44021</v>
-      </c>
-      <c r="I7" s="64"/>
-    </row>
-    <row r="8" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="56">
-        <v>103</v>
-      </c>
-      <c r="I8" s="57"/>
-    </row>
-    <row r="9" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="48"/>
-      <c r="C9" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="67"/>
-      <c r="E9" s="68" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="69"/>
-      <c r="G9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="40">
-        <v>20169138</v>
-      </c>
-      <c r="I9" s="58"/>
-    </row>
-    <row r="10" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="50"/>
-    </row>
-    <row r="11" spans="2:9" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="5" t="s">
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="49" t="s">
+      <c r="H14" s="64"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="71"/>
+    </row>
+    <row r="15" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="81" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B16" s="84" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="85"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="88" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="90" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="40"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="30"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="26"/>
+    </row>
+    <row r="18" spans="2:12" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="73"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="74"/>
+      <c r="K18" s="74"/>
+      <c r="L18" s="75"/>
+    </row>
+    <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="49"/>
-      <c r="G11" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="49"/>
-    </row>
-    <row r="12" spans="2:9" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="49"/>
-      <c r="G12" s="49" t="s">
+      <c r="C19" s="7"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="49"/>
-    </row>
-    <row r="13" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="30">
-        <v>80</v>
-      </c>
-      <c r="H13" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="I13" s="43">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="H14" s="42"/>
-      <c r="I14" s="44"/>
-    </row>
-    <row r="15" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="28"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B16" s="73" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="53"/>
-      <c r="D16" s="54">
-        <v>60000</v>
-      </c>
-      <c r="E16" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="78" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="33"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="74"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="29"/>
-    </row>
-    <row r="18" spans="2:9" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="45"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="50"/>
-    </row>
-    <row r="19" spans="2:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-    </row>
-    <row r="20" spans="2:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I19" s="8"/>
+      <c r="J19" s="76"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="76"/>
+    </row>
+    <row r="20" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="7"/>
-      <c r="C20" s="3"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="8"/>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="2:9" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="2:12" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="40"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="77"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="7"/>
-      <c r="C22" s="3"/>
+      <c r="C22" s="7"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="8"/>
+      <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B23" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="82"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="82"/>
-      <c r="F23" s="82"/>
-      <c r="G23" s="82"/>
-      <c r="H23" s="82"/>
-      <c r="I23" s="83"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B24" s="84"/>
-      <c r="C24" s="85"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="86"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="87"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="88"/>
-      <c r="I25" s="89"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B26" s="87"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="88"/>
-      <c r="I26" s="89"/>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="87"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="89"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="87"/>
-      <c r="C28" s="88"/>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="88"/>
-      <c r="H28" s="88"/>
-      <c r="I28" s="89"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" s="87"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="89"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B30" s="87"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="88"/>
-      <c r="I30" s="89"/>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="87"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="89"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B32" s="87"/>
-      <c r="C32" s="88"/>
-      <c r="D32" s="88"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="88"/>
-      <c r="G32" s="88"/>
-      <c r="H32" s="88"/>
-      <c r="I32" s="89"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B33" s="87"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="89"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B34" s="87"/>
-      <c r="C34" s="88"/>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="88"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B35" s="87"/>
-      <c r="C35" s="88"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="88"/>
-      <c r="G35" s="88"/>
-      <c r="H35" s="88"/>
-      <c r="I35" s="89"/>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B36" s="87"/>
-      <c r="C36" s="88"/>
-      <c r="D36" s="88"/>
-      <c r="E36" s="88"/>
-      <c r="F36" s="88"/>
-      <c r="G36" s="88"/>
-      <c r="H36" s="88"/>
-      <c r="I36" s="89"/>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B37" s="87"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="89"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B38" s="87"/>
-      <c r="C38" s="88"/>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="88"/>
-      <c r="G38" s="88"/>
-      <c r="H38" s="88"/>
-      <c r="I38" s="89"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B39" s="87"/>
-      <c r="C39" s="88"/>
-      <c r="D39" s="88"/>
-      <c r="E39" s="88"/>
-      <c r="F39" s="88"/>
-      <c r="G39" s="88"/>
-      <c r="H39" s="88"/>
-      <c r="I39" s="89"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B40" s="87"/>
-      <c r="C40" s="88"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="88"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="88"/>
-      <c r="H40" s="88"/>
-      <c r="I40" s="89"/>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B41" s="87"/>
-      <c r="C41" s="88"/>
-      <c r="D41" s="88"/>
-      <c r="E41" s="88"/>
-      <c r="F41" s="88"/>
-      <c r="G41" s="88"/>
-      <c r="H41" s="88"/>
-      <c r="I41" s="89"/>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B42" s="87"/>
-      <c r="C42" s="88"/>
-      <c r="D42" s="88"/>
-      <c r="E42" s="88"/>
-      <c r="F42" s="88"/>
-      <c r="G42" s="88"/>
-      <c r="H42" s="88"/>
-      <c r="I42" s="89"/>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B43" s="87"/>
-      <c r="C43" s="88"/>
-      <c r="D43" s="88"/>
-      <c r="E43" s="88"/>
-      <c r="F43" s="88"/>
-      <c r="G43" s="88"/>
-      <c r="H43" s="88"/>
-      <c r="I43" s="89"/>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B44" s="87"/>
-      <c r="C44" s="88"/>
-      <c r="D44" s="88"/>
-      <c r="E44" s="88"/>
-      <c r="F44" s="88"/>
-      <c r="G44" s="88"/>
-      <c r="H44" s="88"/>
-      <c r="I44" s="89"/>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B45" s="87"/>
-      <c r="C45" s="88"/>
-      <c r="D45" s="88"/>
-      <c r="E45" s="88"/>
-      <c r="F45" s="88"/>
-      <c r="G45" s="88"/>
-      <c r="H45" s="88"/>
-      <c r="I45" s="89"/>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B46" s="87"/>
-      <c r="C46" s="88"/>
-      <c r="D46" s="88"/>
-      <c r="E46" s="88"/>
-      <c r="F46" s="88"/>
-      <c r="G46" s="88"/>
-      <c r="H46" s="88"/>
-      <c r="I46" s="89"/>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B47" s="87"/>
-      <c r="C47" s="88"/>
-      <c r="D47" s="88"/>
-      <c r="E47" s="88"/>
-      <c r="F47" s="88"/>
-      <c r="G47" s="88"/>
-      <c r="H47" s="88"/>
-      <c r="I47" s="89"/>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B48" s="87"/>
-      <c r="C48" s="88"/>
-      <c r="D48" s="88"/>
-      <c r="E48" s="88"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="88"/>
-      <c r="H48" s="88"/>
-      <c r="I48" s="89"/>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B49" s="87"/>
-      <c r="C49" s="88"/>
-      <c r="D49" s="88"/>
-      <c r="E49" s="88"/>
-      <c r="F49" s="88"/>
-      <c r="G49" s="88"/>
-      <c r="H49" s="88"/>
-      <c r="I49" s="89"/>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B50" s="90"/>
-      <c r="C50" s="91"/>
-      <c r="D50" s="91"/>
-      <c r="E50" s="91"/>
-      <c r="F50" s="91"/>
-      <c r="G50" s="91"/>
-      <c r="H50" s="91"/>
-      <c r="I50" s="92"/>
-    </row>
-    <row r="51" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="14"/>
-    </row>
-    <row r="52" spans="2:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B23" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="95"/>
+      <c r="D23" s="95"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="95"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="96"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="97"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="99"/>
+      <c r="L24" s="100"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="101"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="103"/>
+      <c r="K25" s="103"/>
+      <c r="L25" s="104"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26" s="101"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="103"/>
+      <c r="L26" s="104"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27" s="101"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="103"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="103"/>
+      <c r="K27" s="103"/>
+      <c r="L27" s="104"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B28" s="101"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="103"/>
+      <c r="H28" s="103"/>
+      <c r="I28" s="103"/>
+      <c r="J28" s="103"/>
+      <c r="K28" s="103"/>
+      <c r="L28" s="104"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29" s="101"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="103"/>
+      <c r="K29" s="103"/>
+      <c r="L29" s="104"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" s="101"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="103"/>
+      <c r="I30" s="103"/>
+      <c r="J30" s="103"/>
+      <c r="K30" s="103"/>
+      <c r="L30" s="104"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="101"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="103"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="103"/>
+      <c r="J31" s="103"/>
+      <c r="K31" s="103"/>
+      <c r="L31" s="104"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B32" s="101"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="103"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="103"/>
+      <c r="J32" s="103"/>
+      <c r="K32" s="103"/>
+      <c r="L32" s="104"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33" s="101"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="103"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="103"/>
+      <c r="J33" s="103"/>
+      <c r="K33" s="103"/>
+      <c r="L33" s="104"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B34" s="101"/>
+      <c r="C34" s="102"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="103"/>
+      <c r="K34" s="103"/>
+      <c r="L34" s="104"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B35" s="101"/>
+      <c r="C35" s="102"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="103"/>
+      <c r="J35" s="103"/>
+      <c r="K35" s="103"/>
+      <c r="L35" s="104"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B36" s="101"/>
+      <c r="C36" s="102"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="103"/>
+      <c r="H36" s="103"/>
+      <c r="I36" s="103"/>
+      <c r="J36" s="103"/>
+      <c r="K36" s="103"/>
+      <c r="L36" s="104"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B37" s="101"/>
+      <c r="C37" s="102"/>
+      <c r="D37" s="103"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="103"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="103"/>
+      <c r="J37" s="103"/>
+      <c r="K37" s="103"/>
+      <c r="L37" s="104"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B38" s="101"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="103"/>
+      <c r="H38" s="103"/>
+      <c r="I38" s="103"/>
+      <c r="J38" s="103"/>
+      <c r="K38" s="103"/>
+      <c r="L38" s="104"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B39" s="101"/>
+      <c r="C39" s="102"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="103"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="103"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="103"/>
+      <c r="J39" s="103"/>
+      <c r="K39" s="103"/>
+      <c r="L39" s="104"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B40" s="101"/>
+      <c r="C40" s="102"/>
+      <c r="D40" s="103"/>
+      <c r="E40" s="103"/>
+      <c r="F40" s="103"/>
+      <c r="G40" s="103"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="103"/>
+      <c r="J40" s="103"/>
+      <c r="K40" s="103"/>
+      <c r="L40" s="104"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B41" s="101"/>
+      <c r="C41" s="102"/>
+      <c r="D41" s="103"/>
+      <c r="E41" s="103"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="103"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="103"/>
+      <c r="J41" s="103"/>
+      <c r="K41" s="103"/>
+      <c r="L41" s="104"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B42" s="101"/>
+      <c r="C42" s="102"/>
+      <c r="D42" s="103"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="103"/>
+      <c r="J42" s="103"/>
+      <c r="K42" s="103"/>
+      <c r="L42" s="104"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B43" s="101"/>
+      <c r="C43" s="102"/>
+      <c r="D43" s="103"/>
+      <c r="E43" s="103"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="103"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="103"/>
+      <c r="J43" s="103"/>
+      <c r="K43" s="103"/>
+      <c r="L43" s="104"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B44" s="101"/>
+      <c r="C44" s="102"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="103"/>
+      <c r="G44" s="103"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="103"/>
+      <c r="J44" s="103"/>
+      <c r="K44" s="103"/>
+      <c r="L44" s="104"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B45" s="101"/>
+      <c r="C45" s="102"/>
+      <c r="D45" s="103"/>
+      <c r="E45" s="103"/>
+      <c r="F45" s="103"/>
+      <c r="G45" s="103"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="103"/>
+      <c r="J45" s="103"/>
+      <c r="K45" s="103"/>
+      <c r="L45" s="104"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B46" s="101"/>
+      <c r="C46" s="102"/>
+      <c r="D46" s="103"/>
+      <c r="E46" s="103"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="103"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="103"/>
+      <c r="J46" s="103"/>
+      <c r="K46" s="103"/>
+      <c r="L46" s="104"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B47" s="101"/>
+      <c r="C47" s="102"/>
+      <c r="D47" s="103"/>
+      <c r="E47" s="103"/>
+      <c r="F47" s="103"/>
+      <c r="G47" s="103"/>
+      <c r="H47" s="103"/>
+      <c r="I47" s="103"/>
+      <c r="J47" s="103"/>
+      <c r="K47" s="103"/>
+      <c r="L47" s="104"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B48" s="101"/>
+      <c r="C48" s="102"/>
+      <c r="D48" s="103"/>
+      <c r="E48" s="103"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="103"/>
+      <c r="J48" s="103"/>
+      <c r="K48" s="103"/>
+      <c r="L48" s="104"/>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B49" s="101"/>
+      <c r="C49" s="102"/>
+      <c r="D49" s="103"/>
+      <c r="E49" s="103"/>
+      <c r="F49" s="103"/>
+      <c r="G49" s="103"/>
+      <c r="H49" s="103"/>
+      <c r="I49" s="103"/>
+      <c r="J49" s="103"/>
+      <c r="K49" s="103"/>
+      <c r="L49" s="104"/>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B50" s="105"/>
+      <c r="C50" s="106"/>
+      <c r="D50" s="106"/>
+      <c r="E50" s="106"/>
+      <c r="F50" s="106"/>
+      <c r="G50" s="106"/>
+      <c r="H50" s="106"/>
+      <c r="I50" s="106"/>
+      <c r="J50" s="106"/>
+      <c r="K50" s="106"/>
+      <c r="L50" s="107"/>
+    </row>
+    <row r="51" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" s="20"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="13"/>
+    </row>
+    <row r="52" spans="2:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C52" s="2"/>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="2"/>
+      <c r="E52" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="I52" s="2"/>
-    </row>
-    <row r="53" spans="2:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J52" s="2"/>
+      <c r="K52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" spans="2:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53" s="34"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="6"/>
-    </row>
-    <row r="54" spans="2:9" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="C54" s="46"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="13"/>
-    </row>
-    <row r="55" spans="2:9" s="6" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="66"/>
-      <c r="C55" s="66"/>
-      <c r="D55" s="66"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="66"/>
-      <c r="G55" s="66"/>
-      <c r="H55" s="66"/>
-      <c r="I55" s="66"/>
-    </row>
-    <row r="56" spans="2:9" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C56" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="D56" s="40"/>
-      <c r="E56" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" s="40"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="24" t="s">
+      <c r="I53" s="2"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" spans="2:12" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="73" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="74"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="74"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="74"/>
+      <c r="L54" s="12"/>
+    </row>
+    <row r="55" spans="2:12" s="6" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="92"/>
+      <c r="C55" s="92"/>
+      <c r="D55" s="92"/>
+      <c r="E55" s="92"/>
+      <c r="F55" s="92"/>
+      <c r="G55" s="92"/>
+      <c r="H55" s="92"/>
+      <c r="I55" s="92"/>
+      <c r="J55" s="92"/>
+      <c r="K55" s="92"/>
+      <c r="L55" s="92"/>
+    </row>
+    <row r="56" spans="2:12" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="46"/>
+      <c r="D56" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="E56" s="64"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H56" s="64"/>
+      <c r="I56" s="64"/>
+      <c r="J56" s="64"/>
+      <c r="K56" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="I56" s="27">
+      <c r="L56" s="24">
         <v>44053</v>
       </c>
     </row>
-    <row r="57" spans="2:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C57" s="2"/>
+    <row r="57" spans="2:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="I57" s="6"/>
-    </row>
-    <row r="58" spans="2:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C58" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="L57" s="6"/>
+    </row>
+    <row r="58" spans="2:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="I58" s="6"/>
-    </row>
-    <row r="59" spans="2:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="2:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F60" s="11" t="s">
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" spans="2:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="2:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I60" s="10"/>
+      <c r="J60" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="G60" s="80" t="s">
-        <v>49</v>
-      </c>
-      <c r="H60" s="80"/>
-      <c r="I60" s="31">
+      <c r="K60" s="93"/>
+      <c r="L60" s="28">
         <v>43616</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="B23:I24"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="B25:I50"/>
-    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="B54:K54"/>
+    <mergeCell ref="B23:L24"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="B25:L50"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="B16:D17"/>
     <mergeCell ref="G16:G17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="B18:L18"/>
+    <mergeCell ref="B2:L4"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="B10:L10"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B2:I4"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -3184,95 +3110,7 @@
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3093" r:id="rId4" name="Check Box 21">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>790575</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>104775</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>2</xdr:col>
-                    <xdr:colOff>180975</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>295275</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="3094" r:id="rId5" name="Check Box 22">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>971550</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>104775</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>1171575</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>295275</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="3095" r:id="rId6" name="Check Box 23">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>1047750</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>104775</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>6</xdr:col>
-                    <xdr:colOff>95250</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>295275</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="3096" r:id="rId7" name="Check Box 24">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>762000</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>114300</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>952500</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>304800</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="3097" r:id="rId8" name="Check Box 25">
+            <control shapeId="3097" r:id="rId4" name="Check Box 25">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3294,7 +3132,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3098" r:id="rId9" name="Check Box 26">
+            <control shapeId="3098" r:id="rId5" name="Check Box 26">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3316,17 +3154,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3099" r:id="rId10" name="Check Box 27">
+            <control shapeId="3099" r:id="rId6" name="Check Box 27">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>4</xdr:col>
+                    <xdr:col>6</xdr:col>
                     <xdr:colOff>238125</xdr:colOff>
                     <xdr:row>9</xdr:row>
                     <xdr:rowOff>238125</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>4</xdr:col>
+                    <xdr:col>6</xdr:col>
                     <xdr:colOff>419100</xdr:colOff>
                     <xdr:row>10</xdr:row>
                     <xdr:rowOff>219075</xdr:rowOff>
@@ -3338,17 +3176,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3100" r:id="rId11" name="Check Box 28">
+            <control shapeId="3100" r:id="rId7" name="Check Box 28">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>4</xdr:col>
+                    <xdr:col>6</xdr:col>
                     <xdr:colOff>238125</xdr:colOff>
                     <xdr:row>11</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>4</xdr:col>
+                    <xdr:col>6</xdr:col>
                     <xdr:colOff>419100</xdr:colOff>
                     <xdr:row>11</xdr:row>
                     <xdr:rowOff>247650</xdr:rowOff>
@@ -3360,17 +3198,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3101" r:id="rId12" name="Check Box 29">
+            <control shapeId="3101" r:id="rId8" name="Check Box 29">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>7</xdr:col>
+                    <xdr:col>10</xdr:col>
                     <xdr:colOff>561975</xdr:colOff>
                     <xdr:row>9</xdr:row>
                     <xdr:rowOff>238125</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>7</xdr:col>
+                    <xdr:col>10</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
                     <xdr:row>10</xdr:row>
                     <xdr:rowOff>219075</xdr:rowOff>
@@ -3382,17 +3220,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3102" r:id="rId13" name="Check Box 30">
+            <control shapeId="3102" r:id="rId9" name="Check Box 30">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>7</xdr:col>
+                    <xdr:col>10</xdr:col>
                     <xdr:colOff>561975</xdr:colOff>
                     <xdr:row>11</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>7</xdr:col>
+                    <xdr:col>10</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
                     <xdr:row>11</xdr:row>
                     <xdr:rowOff>238125</xdr:rowOff>
@@ -3404,17 +3242,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3103" r:id="rId14" name="Check Box 31">
+            <control shapeId="3103" r:id="rId10" name="Check Box 31">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>2</xdr:col>
+                    <xdr:col>3</xdr:col>
                     <xdr:colOff>381000</xdr:colOff>
                     <xdr:row>51</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>2</xdr:col>
+                    <xdr:col>3</xdr:col>
                     <xdr:colOff>561975</xdr:colOff>
                     <xdr:row>52</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
@@ -3426,17 +3264,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3106" r:id="rId15" name="Check Box 34">
+            <control shapeId="3106" r:id="rId11" name="Check Box 34">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>4</xdr:col>
+                    <xdr:col>6</xdr:col>
                     <xdr:colOff>219075</xdr:colOff>
                     <xdr:row>51</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>4</xdr:col>
+                    <xdr:col>6</xdr:col>
                     <xdr:colOff>409575</xdr:colOff>
                     <xdr:row>52</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
@@ -3448,17 +3286,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3107" r:id="rId16" name="Check Box 35">
+            <control shapeId="3107" r:id="rId12" name="Check Box 35">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>6</xdr:col>
+                    <xdr:col>9</xdr:col>
                     <xdr:colOff>533400</xdr:colOff>
                     <xdr:row>51</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>6</xdr:col>
+                    <xdr:col>9</xdr:col>
                     <xdr:colOff>695325</xdr:colOff>
                     <xdr:row>52</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
@@ -3470,17 +3308,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3110" r:id="rId17" name="Check Box 38">
+            <control shapeId="3110" r:id="rId13" name="Check Box 38">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>2</xdr:col>
+                    <xdr:col>3</xdr:col>
                     <xdr:colOff>381000</xdr:colOff>
                     <xdr:row>52</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>2</xdr:col>
+                    <xdr:col>3</xdr:col>
                     <xdr:colOff>561975</xdr:colOff>
                     <xdr:row>53</xdr:row>
                     <xdr:rowOff>28575</xdr:rowOff>
@@ -3492,17 +3330,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3111" r:id="rId18" name="Check Box 39">
+            <control shapeId="3111" r:id="rId14" name="Check Box 39">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>4</xdr:col>
+                    <xdr:col>6</xdr:col>
                     <xdr:colOff>219075</xdr:colOff>
                     <xdr:row>52</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>4</xdr:col>
+                    <xdr:col>6</xdr:col>
                     <xdr:colOff>409575</xdr:colOff>
                     <xdr:row>53</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
@@ -3514,17 +3352,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3112" r:id="rId19" name="Check Box 40">
+            <control shapeId="3112" r:id="rId15" name="Check Box 40">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>6</xdr:col>
+                    <xdr:col>9</xdr:col>
                     <xdr:colOff>533400</xdr:colOff>
                     <xdr:row>52</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>6</xdr:col>
+                    <xdr:col>9</xdr:col>
                     <xdr:colOff>723900</xdr:colOff>
                     <xdr:row>53</xdr:row>
                     <xdr:rowOff>9525</xdr:rowOff>
@@ -3536,18 +3374,18 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3113" r:id="rId20" name="Check Box 41">
+            <control shapeId="3113" r:id="rId16" name="Check Box 41">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>7</xdr:col>
+                    <xdr:col>10</xdr:col>
                     <xdr:colOff>666750</xdr:colOff>
                     <xdr:row>51</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>828675</xdr:colOff>
+                    <xdr:col>11</xdr:col>
+                    <xdr:colOff>47625</xdr:colOff>
                     <xdr:row>51</xdr:row>
                     <xdr:rowOff>200025</xdr:rowOff>
                   </to>
@@ -3558,17 +3396,17 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="3117" r:id="rId21" name="Check Box 45">
+            <control shapeId="3117" r:id="rId17" name="Check Box 45">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>4</xdr:col>
+                    <xdr:col>6</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>15</xdr:row>
                     <xdr:rowOff>47625</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>4</xdr:col>
+                    <xdr:col>6</xdr:col>
                     <xdr:colOff>466725</xdr:colOff>
                     <xdr:row>16</xdr:row>
                     <xdr:rowOff>104775</xdr:rowOff>
@@ -3585,18 +3423,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MediaLengthInSeconds xmlns="8fb20e23-5003-4e3a-b5f0-652bad7298ae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8fb20e23-5003-4e3a-b5f0-652bad7298ae">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3f6fd112-63a3-475d-82b8-980e7b6442a9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3605,7 +3431,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009487DF3248FCD549B5D95C6664C039A6" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="085837f79abe65ad6c2ca97b2fb61ff5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8fb20e23-5003-4e3a-b5f0-652bad7298ae" xmlns:ns3="3f6fd112-63a3-475d-82b8-980e7b6442a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a391c53ee0622473d16f9083755cc4a" ns2:_="" ns3:_="">
     <xsd:import namespace="8fb20e23-5003-4e3a-b5f0-652bad7298ae"/>
@@ -3834,18 +3660,19 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1B3EA31-4F48-4CEB-99C4-AF763929DE31}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8fb20e23-5003-4e3a-b5f0-652bad7298ae"/>
-    <ds:schemaRef ds:uri="3f6fd112-63a3-475d-82b8-980e7b6442a9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MediaLengthInSeconds xmlns="8fb20e23-5003-4e3a-b5f0-652bad7298ae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8fb20e23-5003-4e3a-b5f0-652bad7298ae">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3f6fd112-63a3-475d-82b8-980e7b6442a9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EB2665B-706A-4D48-A87F-78C735B6EB0C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3853,7 +3680,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53CC8395-CA98-4BC9-9578-D8F1DE7BBF4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3870,4 +3697,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1B3EA31-4F48-4CEB-99C4-AF763929DE31}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8fb20e23-5003-4e3a-b5f0-652bad7298ae"/>
+    <ds:schemaRef ds:uri="3f6fd112-63a3-475d-82b8-980e7b6442a9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/FIIN.xlsx
+++ b/FIIN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme\OneDrive\Desktop\gui\Programas\python\ExcelPython\Mehtal_v.1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C63FBA-8DFB-4185-B2E7-A5CD53697551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1696091B-8BAE-4B6F-A612-0A475521ACE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>UTIÇLIZA</t>
   </si>
   <si>
-    <t>Volume anual: 13.266</t>
-  </si>
-  <si>
     <t xml:space="preserve">Methal Company: </t>
   </si>
   <si>
@@ -204,6 +201,9 @@
   </si>
   <si>
     <t xml:space="preserve">Localização:  </t>
+  </si>
+  <si>
+    <t>Volume anual:</t>
   </si>
 </sst>
 </file>
@@ -559,6 +559,150 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -589,157 +733,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2196,304 +2196,304 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
     </row>
     <row r="3" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
     </row>
     <row r="4" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="95"/>
+      <c r="L4" s="95"/>
     </row>
     <row r="5" spans="2:18" s="6" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B5" s="52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="20"/>
       <c r="E5" s="51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" s="50"/>
       <c r="G5" s="12"/>
       <c r="H5" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="50"/>
+      <c r="J5" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="50"/>
-      <c r="J5" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="57"/>
+      <c r="K5" s="105"/>
       <c r="L5" s="50"/>
     </row>
     <row r="6" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="63"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="111"/>
       <c r="G6" s="16" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="42"/>
       <c r="I6" s="48"/>
       <c r="J6" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="K6" s="109"/>
-      <c r="L6" s="110"/>
+        <v>54</v>
+      </c>
+      <c r="K6" s="87"/>
+      <c r="L6" s="88"/>
     </row>
     <row r="7" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="112"/>
       <c r="G7" s="44" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="113" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="114"/>
-      <c r="K7" s="109"/>
-      <c r="L7" s="110"/>
+      <c r="I7" s="91" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="92"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="88"/>
       <c r="Q7" s="7"/>
     </row>
     <row r="8" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="59"/>
+      <c r="B8" s="106" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="107"/>
       <c r="D8" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="54"/>
-      <c r="F8" s="55"/>
+        <v>44</v>
+      </c>
+      <c r="E8" s="102"/>
+      <c r="F8" s="103"/>
       <c r="G8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="108"/>
+      <c r="H8" s="54"/>
       <c r="I8" s="49"/>
       <c r="J8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="109"/>
-      <c r="L8" s="110"/>
+      <c r="K8" s="87"/>
+      <c r="L8" s="88"/>
     </row>
     <row r="9" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="60"/>
-      <c r="C9" s="61"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="109"/>
       <c r="D9" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="54"/>
-      <c r="F9" s="55"/>
+        <v>45</v>
+      </c>
+      <c r="E9" s="102"/>
+      <c r="F9" s="103"/>
       <c r="G9" s="53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H9" s="45"/>
       <c r="I9" s="39"/>
       <c r="J9" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="111"/>
-      <c r="L9" s="112"/>
+        <v>52</v>
+      </c>
+      <c r="K9" s="89"/>
+      <c r="L9" s="90"/>
       <c r="R9" s="7"/>
     </row>
     <row r="10" spans="2:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="73" t="s">
+      <c r="B10" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="75"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
+      <c r="K10" s="58"/>
+      <c r="L10" s="94"/>
     </row>
     <row r="11" spans="2:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="35"/>
-      <c r="E11" s="72" t="s">
+      <c r="E11" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="J11" s="72" t="s">
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="J11" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="K11" s="72"/>
+      <c r="K11" s="101"/>
     </row>
     <row r="12" spans="2:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="E12" s="72" t="s">
+      <c r="E12" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="J12" s="72" t="s">
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="J12" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="72"/>
+      <c r="K12" s="101"/>
     </row>
     <row r="13" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
       <c r="E13" s="17"/>
       <c r="F13" s="47"/>
-      <c r="G13" s="67" t="s">
+      <c r="G13" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="64"/>
+      <c r="H13" s="66"/>
       <c r="I13" s="33"/>
       <c r="J13" s="27"/>
-      <c r="K13" s="68" t="s">
+      <c r="K13" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="70"/>
+      <c r="L13" s="99"/>
     </row>
     <row r="14" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
       <c r="E14" s="17"/>
       <c r="F14" s="47"/>
-      <c r="G14" s="67" t="s">
+      <c r="G14" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="64"/>
+      <c r="H14" s="66"/>
       <c r="I14" s="33"/>
       <c r="J14" s="18"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="71"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="100"/>
     </row>
     <row r="15" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
+      <c r="B15" s="106" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="114"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
       <c r="I15" s="38"/>
       <c r="J15" s="29"/>
       <c r="K15" s="32"/>
       <c r="L15" s="25"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="85"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="79"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="85"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="88" t="s">
+      <c r="G16" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="90" t="s">
+      <c r="H16" s="82" t="s">
         <v>37</v>
       </c>
       <c r="I16" s="40"/>
-      <c r="J16" s="78"/>
+      <c r="J16" s="77"/>
       <c r="K16" s="31"/>
       <c r="L16" s="30"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B17" s="86"/>
-      <c r="C17" s="87"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="80"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="86"/>
       <c r="F17" s="37"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="91"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="83"/>
       <c r="I17" s="41"/>
-      <c r="J17" s="77"/>
+      <c r="J17" s="84"/>
       <c r="K17" s="9"/>
       <c r="L17" s="26"/>
     </row>
     <row r="18" spans="2:12" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="73"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="74"/>
-      <c r="L18" s="75"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="94"/>
     </row>
     <row r="19" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="7"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
       <c r="H19" s="8" t="s">
         <v>26</v>
       </c>
       <c r="I19" s="8"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
+      <c r="J19" s="93"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="93"/>
     </row>
     <row r="20" spans="2:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="7"/>
@@ -2513,17 +2513,17 @@
         <v>25</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="84"/>
+      <c r="G21" s="84"/>
       <c r="H21" s="19" t="s">
         <v>27</v>
       </c>
       <c r="I21" s="40"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="77"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="7"/>
@@ -2539,370 +2539,370 @@
       <c r="L22" s="3"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="95"/>
-      <c r="D23" s="95"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="95"/>
-      <c r="H23" s="95"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="95"/>
-      <c r="L23" s="96"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="61"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="97"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="100"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="65"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="101"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="103"/>
-      <c r="K25" s="103"/>
-      <c r="L25" s="104"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="70"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B26" s="101"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="103"/>
-      <c r="K26" s="103"/>
-      <c r="L26" s="104"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="70"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B27" s="101"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="103"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="103"/>
-      <c r="L27" s="104"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="70"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="101"/>
-      <c r="C28" s="102"/>
-      <c r="D28" s="103"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="103"/>
-      <c r="G28" s="103"/>
-      <c r="H28" s="103"/>
-      <c r="I28" s="103"/>
-      <c r="J28" s="103"/>
-      <c r="K28" s="103"/>
-      <c r="L28" s="104"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="70"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="101"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="103"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="103"/>
-      <c r="G29" s="103"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="103"/>
-      <c r="J29" s="103"/>
-      <c r="K29" s="103"/>
-      <c r="L29" s="104"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="69"/>
+      <c r="L29" s="70"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B30" s="101"/>
-      <c r="C30" s="102"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="103"/>
-      <c r="G30" s="103"/>
-      <c r="H30" s="103"/>
-      <c r="I30" s="103"/>
-      <c r="J30" s="103"/>
-      <c r="K30" s="103"/>
-      <c r="L30" s="104"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="70"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B31" s="101"/>
-      <c r="C31" s="102"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="103"/>
-      <c r="G31" s="103"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="103"/>
-      <c r="J31" s="103"/>
-      <c r="K31" s="103"/>
-      <c r="L31" s="104"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="70"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B32" s="101"/>
-      <c r="C32" s="102"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="103"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="103"/>
-      <c r="I32" s="103"/>
-      <c r="J32" s="103"/>
-      <c r="K32" s="103"/>
-      <c r="L32" s="104"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="69"/>
+      <c r="L32" s="70"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="101"/>
-      <c r="C33" s="102"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="103"/>
-      <c r="G33" s="103"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="103"/>
-      <c r="J33" s="103"/>
-      <c r="K33" s="103"/>
-      <c r="L33" s="104"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="69"/>
+      <c r="L33" s="70"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="101"/>
-      <c r="C34" s="102"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="103"/>
-      <c r="F34" s="103"/>
-      <c r="G34" s="103"/>
-      <c r="H34" s="103"/>
-      <c r="I34" s="103"/>
-      <c r="J34" s="103"/>
-      <c r="K34" s="103"/>
-      <c r="L34" s="104"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="69"/>
+      <c r="K34" s="69"/>
+      <c r="L34" s="70"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="101"/>
-      <c r="C35" s="102"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="103"/>
-      <c r="J35" s="103"/>
-      <c r="K35" s="103"/>
-      <c r="L35" s="104"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
+      <c r="L35" s="70"/>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B36" s="101"/>
-      <c r="C36" s="102"/>
-      <c r="D36" s="103"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="103"/>
-      <c r="G36" s="103"/>
-      <c r="H36" s="103"/>
-      <c r="I36" s="103"/>
-      <c r="J36" s="103"/>
-      <c r="K36" s="103"/>
-      <c r="L36" s="104"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="69"/>
+      <c r="L36" s="70"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B37" s="101"/>
-      <c r="C37" s="102"/>
-      <c r="D37" s="103"/>
-      <c r="E37" s="103"/>
-      <c r="F37" s="103"/>
-      <c r="G37" s="103"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="103"/>
-      <c r="J37" s="103"/>
-      <c r="K37" s="103"/>
-      <c r="L37" s="104"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="68"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="70"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B38" s="101"/>
-      <c r="C38" s="102"/>
-      <c r="D38" s="103"/>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="103"/>
-      <c r="H38" s="103"/>
-      <c r="I38" s="103"/>
-      <c r="J38" s="103"/>
-      <c r="K38" s="103"/>
-      <c r="L38" s="104"/>
+      <c r="B38" s="67"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="69"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="70"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B39" s="101"/>
-      <c r="C39" s="102"/>
-      <c r="D39" s="103"/>
-      <c r="E39" s="103"/>
-      <c r="F39" s="103"/>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="103"/>
-      <c r="J39" s="103"/>
-      <c r="K39" s="103"/>
-      <c r="L39" s="104"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
+      <c r="L39" s="70"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B40" s="101"/>
-      <c r="C40" s="102"/>
-      <c r="D40" s="103"/>
-      <c r="E40" s="103"/>
-      <c r="F40" s="103"/>
-      <c r="G40" s="103"/>
-      <c r="H40" s="103"/>
-      <c r="I40" s="103"/>
-      <c r="J40" s="103"/>
-      <c r="K40" s="103"/>
-      <c r="L40" s="104"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="68"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="69"/>
+      <c r="L40" s="70"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B41" s="101"/>
-      <c r="C41" s="102"/>
-      <c r="D41" s="103"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="103"/>
-      <c r="H41" s="103"/>
-      <c r="I41" s="103"/>
-      <c r="J41" s="103"/>
-      <c r="K41" s="103"/>
-      <c r="L41" s="104"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="70"/>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B42" s="101"/>
-      <c r="C42" s="102"/>
-      <c r="D42" s="103"/>
-      <c r="E42" s="103"/>
-      <c r="F42" s="103"/>
-      <c r="G42" s="103"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="103"/>
-      <c r="J42" s="103"/>
-      <c r="K42" s="103"/>
-      <c r="L42" s="104"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="69"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="69"/>
+      <c r="K42" s="69"/>
+      <c r="L42" s="70"/>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B43" s="101"/>
-      <c r="C43" s="102"/>
-      <c r="D43" s="103"/>
-      <c r="E43" s="103"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="103"/>
-      <c r="H43" s="103"/>
-      <c r="I43" s="103"/>
-      <c r="J43" s="103"/>
-      <c r="K43" s="103"/>
-      <c r="L43" s="104"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="69"/>
+      <c r="K43" s="69"/>
+      <c r="L43" s="70"/>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B44" s="101"/>
-      <c r="C44" s="102"/>
-      <c r="D44" s="103"/>
-      <c r="E44" s="103"/>
-      <c r="F44" s="103"/>
-      <c r="G44" s="103"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="103"/>
-      <c r="J44" s="103"/>
-      <c r="K44" s="103"/>
-      <c r="L44" s="104"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="69"/>
+      <c r="L44" s="70"/>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B45" s="101"/>
-      <c r="C45" s="102"/>
-      <c r="D45" s="103"/>
-      <c r="E45" s="103"/>
-      <c r="F45" s="103"/>
-      <c r="G45" s="103"/>
-      <c r="H45" s="103"/>
-      <c r="I45" s="103"/>
-      <c r="J45" s="103"/>
-      <c r="K45" s="103"/>
-      <c r="L45" s="104"/>
+      <c r="B45" s="67"/>
+      <c r="C45" s="68"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
+      <c r="K45" s="69"/>
+      <c r="L45" s="70"/>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B46" s="101"/>
-      <c r="C46" s="102"/>
-      <c r="D46" s="103"/>
-      <c r="E46" s="103"/>
-      <c r="F46" s="103"/>
-      <c r="G46" s="103"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="103"/>
-      <c r="J46" s="103"/>
-      <c r="K46" s="103"/>
-      <c r="L46" s="104"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
+      <c r="L46" s="70"/>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B47" s="101"/>
-      <c r="C47" s="102"/>
-      <c r="D47" s="103"/>
-      <c r="E47" s="103"/>
-      <c r="F47" s="103"/>
-      <c r="G47" s="103"/>
-      <c r="H47" s="103"/>
-      <c r="I47" s="103"/>
-      <c r="J47" s="103"/>
-      <c r="K47" s="103"/>
-      <c r="L47" s="104"/>
+      <c r="B47" s="67"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="70"/>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B48" s="101"/>
-      <c r="C48" s="102"/>
-      <c r="D48" s="103"/>
-      <c r="E48" s="103"/>
-      <c r="F48" s="103"/>
-      <c r="G48" s="103"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="103"/>
-      <c r="J48" s="103"/>
-      <c r="K48" s="103"/>
-      <c r="L48" s="104"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
+      <c r="L48" s="70"/>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B49" s="101"/>
-      <c r="C49" s="102"/>
-      <c r="D49" s="103"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="103"/>
-      <c r="G49" s="103"/>
-      <c r="H49" s="103"/>
-      <c r="I49" s="103"/>
-      <c r="J49" s="103"/>
-      <c r="K49" s="103"/>
-      <c r="L49" s="104"/>
+      <c r="B49" s="67"/>
+      <c r="C49" s="68"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="70"/>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B50" s="105"/>
-      <c r="C50" s="106"/>
-      <c r="D50" s="106"/>
-      <c r="E50" s="106"/>
-      <c r="F50" s="106"/>
-      <c r="G50" s="106"/>
-      <c r="H50" s="106"/>
-      <c r="I50" s="106"/>
-      <c r="J50" s="106"/>
-      <c r="K50" s="106"/>
-      <c r="L50" s="107"/>
+      <c r="B50" s="71"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="72"/>
+      <c r="F50" s="72"/>
+      <c r="G50" s="72"/>
+      <c r="H50" s="72"/>
+      <c r="I50" s="72"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="72"/>
+      <c r="L50" s="73"/>
     </row>
     <row r="51" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="15" t="s">
@@ -2960,49 +2960,49 @@
       <c r="L53" s="6"/>
     </row>
     <row r="54" spans="2:12" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="73" t="s">
+      <c r="B54" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C54" s="74"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="74"/>
-      <c r="I54" s="74"/>
-      <c r="J54" s="74"/>
-      <c r="K54" s="74"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="58"/>
+      <c r="I54" s="58"/>
+      <c r="J54" s="58"/>
+      <c r="K54" s="58"/>
       <c r="L54" s="12"/>
     </row>
     <row r="55" spans="2:12" s="6" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="92"/>
-      <c r="C55" s="92"/>
-      <c r="D55" s="92"/>
-      <c r="E55" s="92"/>
-      <c r="F55" s="92"/>
-      <c r="G55" s="92"/>
-      <c r="H55" s="92"/>
-      <c r="I55" s="92"/>
-      <c r="J55" s="92"/>
-      <c r="K55" s="92"/>
-      <c r="L55" s="92"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="55"/>
+      <c r="D55" s="55"/>
+      <c r="E55" s="55"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="55"/>
+      <c r="J55" s="55"/>
+      <c r="K55" s="55"/>
+      <c r="L55" s="55"/>
     </row>
     <row r="56" spans="2:12" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="22" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="46"/>
-      <c r="D56" s="64" t="s">
+      <c r="D56" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="E56" s="64"/>
+      <c r="E56" s="66"/>
       <c r="F56" s="33"/>
       <c r="G56" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="H56" s="64"/>
-      <c r="I56" s="64"/>
-      <c r="J56" s="64"/>
+      <c r="H56" s="66"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="66"/>
       <c r="K56" s="21" t="s">
         <v>0</v>
       </c>
@@ -3048,39 +3048,20 @@
         <v>34</v>
       </c>
       <c r="I60" s="10"/>
-      <c r="J60" s="93" t="s">
+      <c r="J60" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="K60" s="93"/>
+      <c r="K60" s="56"/>
       <c r="L60" s="28">
         <v>43616</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="B55:L55"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="B54:K54"/>
-    <mergeCell ref="B23:L24"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="B25:L50"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="B16:D17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="B18:L18"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="B2:L4"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="K13:K14"/>
@@ -3097,9 +3078,28 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B8:C9"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="B18:L18"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="B16:D17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="B54:K54"/>
+    <mergeCell ref="B23:L24"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="B25:L50"/>
+    <mergeCell ref="D56:E56"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -3423,15 +3423,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009487DF3248FCD549B5D95C6664C039A6" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="085837f79abe65ad6c2ca97b2fb61ff5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8fb20e23-5003-4e3a-b5f0-652bad7298ae" xmlns:ns3="3f6fd112-63a3-475d-82b8-980e7b6442a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a391c53ee0622473d16f9083755cc4a" ns2:_="" ns3:_="">
     <xsd:import namespace="8fb20e23-5003-4e3a-b5f0-652bad7298ae"/>
@@ -3660,6 +3651,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3673,14 +3673,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EB2665B-706A-4D48-A87F-78C735B6EB0C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53CC8395-CA98-4BC9-9578-D8F1DE7BBF4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3699,6 +3691,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EB2665B-706A-4D48-A87F-78C735B6EB0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1B3EA31-4F48-4CEB-99C4-AF763929DE31}">
   <ds:schemaRefs>
